--- a/artfynd/A 5185-2024 artfynd.xlsx
+++ b/artfynd/A 5185-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120159827</v>
+        <v>120159831</v>
       </c>
       <c r="B2" t="n">
-        <v>106443</v>
+        <v>77866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>6443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120159831</v>
+        <v>120159827</v>
       </c>
       <c r="B3" t="n">
-        <v>77866</v>
+        <v>106443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6443</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 5185-2024 artfynd.xlsx
+++ b/artfynd/A 5185-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120159831</v>
       </c>
       <c r="B2" t="n">
-        <v>77866</v>
+        <v>77882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>120159827</v>
       </c>
       <c r="B3" t="n">
-        <v>106443</v>
+        <v>106467</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 5185-2024 artfynd.xlsx
+++ b/artfynd/A 5185-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120159831</v>
+        <v>120159827</v>
       </c>
       <c r="B2" t="n">
-        <v>77882</v>
+        <v>106467</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6443</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120159827</v>
+        <v>120159831</v>
       </c>
       <c r="B3" t="n">
-        <v>106467</v>
+        <v>77882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>6443</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 5185-2024 artfynd.xlsx
+++ b/artfynd/A 5185-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120159827</v>
+        <v>120159831</v>
       </c>
       <c r="B2" t="n">
-        <v>106467</v>
+        <v>77882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>6443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120159831</v>
+        <v>120159827</v>
       </c>
       <c r="B3" t="n">
-        <v>77882</v>
+        <v>106467</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6443</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
